--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_01-06-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_01-06-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Celotex_Prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9A513C4-CC74-46B8-8737-E411498C1A5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BBFBBB6-B9E5-4E79-AF64-75639175A473}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4305" yWindow="2715" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33990" yWindow="270" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1117,9 +1117,6 @@
     <t>£2208.32</t>
   </si>
   <si>
-    <t>£128.48</t>
-  </si>
-  <si>
     <t>£1841.92</t>
   </si>
   <si>
@@ -1156,9 +1153,6 @@
     <t>£2057.12</t>
   </si>
   <si>
-    <t>£177.92</t>
-  </si>
-  <si>
     <t>£2050.88</t>
   </si>
   <si>
@@ -1192,9 +1186,6 @@
     <t>£2183.04</t>
   </si>
   <si>
-    <t>£199.16</t>
-  </si>
-  <si>
     <t>£2087.52</t>
   </si>
   <si>
@@ -1202,6 +1193,15 @@
   </si>
   <si>
     <t>£2265.12</t>
+  </si>
+  <si>
+    <t>£2055.68</t>
+  </si>
+  <si>
+    <t>£2846.72</t>
+  </si>
+  <si>
+    <t>£3186.56</t>
   </si>
 </sst>
 </file>
@@ -3064,131 +3064,131 @@
         <v>364</v>
       </c>
       <c r="N27" t="s">
+        <v>391</v>
+      </c>
+      <c r="O27" t="s">
         <v>365</v>
       </c>
-      <c r="O27" t="s">
+      <c r="P27" t="s">
         <v>366</v>
       </c>
-      <c r="P27" t="s">
+      <c r="Q27" t="s">
         <v>367</v>
       </c>
-      <c r="Q27" t="s">
+      <c r="R27" t="s">
         <v>368</v>
-      </c>
-      <c r="R27" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>369</v>
+      </c>
+      <c r="B28" t="s">
         <v>370</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C28" t="s">
         <v>371</v>
       </c>
-      <c r="C28" t="s">
+      <c r="D28" t="s">
+        <v>371</v>
+      </c>
+      <c r="E28" t="s">
+        <v>371</v>
+      </c>
+      <c r="F28" t="s">
         <v>372</v>
-      </c>
-      <c r="D28" t="s">
-        <v>372</v>
-      </c>
-      <c r="E28" t="s">
-        <v>372</v>
-      </c>
-      <c r="F28" t="s">
-        <v>373</v>
       </c>
       <c r="G28" t="s">
         <v>160</v>
       </c>
       <c r="H28" t="s">
+        <v>373</v>
+      </c>
+      <c r="I28" t="s">
         <v>374</v>
-      </c>
-      <c r="I28" t="s">
-        <v>375</v>
       </c>
       <c r="J28" t="s">
         <v>160</v>
       </c>
       <c r="K28" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="L28" t="s">
         <v>27</v>
       </c>
       <c r="M28" t="s">
+        <v>376</v>
+      </c>
+      <c r="N28" t="s">
+        <v>392</v>
+      </c>
+      <c r="O28" t="s">
         <v>377</v>
       </c>
-      <c r="N28" t="s">
+      <c r="P28" t="s">
         <v>378</v>
       </c>
-      <c r="O28" t="s">
+      <c r="Q28" t="s">
         <v>379</v>
       </c>
-      <c r="P28" t="s">
+      <c r="R28" t="s">
         <v>380</v>
-      </c>
-      <c r="Q28" t="s">
-        <v>381</v>
-      </c>
-      <c r="R28" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>381</v>
+      </c>
+      <c r="B29" t="s">
+        <v>382</v>
+      </c>
+      <c r="C29" t="s">
         <v>383</v>
       </c>
-      <c r="B29" t="s">
-        <v>384</v>
-      </c>
-      <c r="C29" t="s">
-        <v>385</v>
-      </c>
       <c r="D29" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="E29" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="F29" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="G29" t="s">
         <v>160</v>
       </c>
       <c r="H29" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="I29" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="J29" t="s">
         <v>160</v>
       </c>
       <c r="K29" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="L29" t="s">
         <v>160</v>
       </c>
       <c r="M29" t="s">
+        <v>387</v>
+      </c>
+      <c r="N29" t="s">
+        <v>393</v>
+      </c>
+      <c r="O29" t="s">
+        <v>388</v>
+      </c>
+      <c r="P29" t="s">
         <v>389</v>
-      </c>
-      <c r="N29" t="s">
-        <v>390</v>
-      </c>
-      <c r="O29" t="s">
-        <v>391</v>
-      </c>
-      <c r="P29" t="s">
-        <v>392</v>
       </c>
       <c r="Q29" t="s">
         <v>160</v>
       </c>
       <c r="R29" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
     </row>
   </sheetData>
